--- a/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_ALIMERKA OVIEDO BALONCESTO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_ALIMERKA OVIEDO BALONCESTO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. COSIALLS BORRAS</t>
+          <t>M. TOWNES VILLAR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
-        <v>67.16670000000001</v>
+        <v>57.0615</v>
       </c>
       <c r="E2" t="n">
-        <v>59.3135</v>
+        <v>28.4267</v>
       </c>
       <c r="F2" t="n">
-        <v>7.853600000000001</v>
+        <v>28.6346</v>
       </c>
       <c r="G2" t="n">
-        <v>18.7094</v>
+        <v>52.6901</v>
       </c>
       <c r="H2" t="n">
-        <v>7.1936</v>
+        <v>4.7974</v>
       </c>
       <c r="I2" t="n">
-        <v>11.5157</v>
+        <v>47.8925</v>
       </c>
       <c r="J2" t="n">
-        <v>39.665</v>
+        <v>72.1253</v>
       </c>
       <c r="K2" t="n">
-        <v>18.3905</v>
+        <v>20.4442</v>
       </c>
       <c r="L2" t="n">
-        <v>21.2744</v>
+        <v>51.6815</v>
       </c>
       <c r="M2" t="n">
-        <v>-20.9557</v>
+        <v>-19.4355</v>
       </c>
       <c r="N2" t="n">
-        <v>-11.1965</v>
+        <v>-15.6465</v>
       </c>
       <c r="O2" t="n">
-        <v>-9.758600000000001</v>
+        <v>-3.789000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>9.3528</v>
+        <v>-36.9763</v>
       </c>
       <c r="Q2" t="n">
-        <v>-32.6258</v>
+        <v>-93.093</v>
       </c>
       <c r="R2" t="n">
-        <v>41.9787</v>
+        <v>56.117</v>
       </c>
       <c r="S2" t="n">
-        <v>49.1055</v>
+        <v>10.1991</v>
       </c>
       <c r="T2" t="n">
-        <v>38.5904</v>
+        <v>2.0985</v>
       </c>
       <c r="U2" t="n">
-        <v>10.5151</v>
+        <v>8.1006</v>
       </c>
       <c r="V2" t="n">
-        <v>-10.0011</v>
+        <v>31.1487</v>
       </c>
       <c r="W2" t="n">
-        <v>13.6838</v>
+        <v>47.2959</v>
       </c>
       <c r="X2" t="n">
-        <v>-23.6848</v>
+        <v>-16.1472</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. TOWNES VILLAR</t>
+          <t>R. COSIALLS BORRAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D3" t="n">
-        <v>47.8408</v>
+        <v>41.8433</v>
       </c>
       <c r="E3" t="n">
-        <v>16.422</v>
+        <v>34.8782</v>
       </c>
       <c r="F3" t="n">
-        <v>31.4188</v>
+        <v>6.9654</v>
       </c>
       <c r="G3" t="n">
-        <v>52.6901</v>
+        <v>18.7094</v>
       </c>
       <c r="H3" t="n">
-        <v>4.7974</v>
+        <v>7.1936</v>
       </c>
       <c r="I3" t="n">
-        <v>47.8925</v>
+        <v>11.5157</v>
       </c>
       <c r="J3" t="n">
-        <v>72.1253</v>
+        <v>39.665</v>
       </c>
       <c r="K3" t="n">
-        <v>20.4442</v>
+        <v>18.3905</v>
       </c>
       <c r="L3" t="n">
-        <v>51.6815</v>
+        <v>21.2744</v>
       </c>
       <c r="M3" t="n">
-        <v>-19.4355</v>
+        <v>-20.9557</v>
       </c>
       <c r="N3" t="n">
-        <v>-15.6465</v>
+        <v>-11.1965</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.789000000000001</v>
+        <v>-9.758600000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>-36.9763</v>
+        <v>9.3528</v>
       </c>
       <c r="Q3" t="n">
-        <v>-93.093</v>
+        <v>-32.6258</v>
       </c>
       <c r="R3" t="n">
-        <v>56.117</v>
+        <v>41.9787</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9784999999999999</v>
+        <v>23.7819</v>
       </c>
       <c r="T3" t="n">
-        <v>-9.9064</v>
+        <v>14.1551</v>
       </c>
       <c r="U3" t="n">
-        <v>10.8849</v>
+        <v>9.627000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>31.1487</v>
+        <v>-10.0011</v>
       </c>
       <c r="W3" t="n">
-        <v>47.2959</v>
+        <v>13.6838</v>
       </c>
       <c r="X3" t="n">
-        <v>-16.1472</v>
+        <v>-23.6848</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. FAURE RIBES</t>
+          <t>R. LOBACO MUÑOZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
-        <v>38.5129</v>
+        <v>36.2191</v>
       </c>
       <c r="E4" t="n">
-        <v>23.2075</v>
+        <v>13.8462</v>
       </c>
       <c r="F4" t="n">
-        <v>15.3053</v>
+        <v>22.3727</v>
       </c>
       <c r="G4" t="n">
-        <v>19.4361</v>
+        <v>1.528900000000002</v>
       </c>
       <c r="H4" t="n">
-        <v>13.358</v>
+        <v>-8.369400000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>6.0782</v>
+        <v>9.898300000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>38.2164</v>
+        <v>33.4754</v>
       </c>
       <c r="K4" t="n">
-        <v>25.072</v>
+        <v>12.0736</v>
       </c>
       <c r="L4" t="n">
-        <v>13.1438</v>
+        <v>21.402</v>
       </c>
       <c r="M4" t="n">
-        <v>-18.7801</v>
+        <v>-31.9465</v>
       </c>
       <c r="N4" t="n">
-        <v>-11.7141</v>
+        <v>-20.4432</v>
       </c>
       <c r="O4" t="n">
-        <v>-7.0662</v>
+        <v>-11.5034</v>
       </c>
       <c r="P4" t="n">
-        <v>-10.8754</v>
+        <v>18.4882</v>
       </c>
       <c r="Q4" t="n">
-        <v>-50.2438</v>
+        <v>-44.3713</v>
       </c>
       <c r="R4" t="n">
-        <v>39.3683</v>
+        <v>62.8595</v>
       </c>
       <c r="S4" t="n">
-        <v>40.1379</v>
+        <v>11.6454</v>
       </c>
       <c r="T4" t="n">
-        <v>24.2935</v>
+        <v>2.2343</v>
       </c>
       <c r="U4" t="n">
-        <v>15.8444</v>
+        <v>9.4109</v>
       </c>
       <c r="V4" t="n">
-        <v>-10.1856</v>
+        <v>4.5565</v>
       </c>
       <c r="W4" t="n">
-        <v>10.9412</v>
+        <v>22.5076</v>
       </c>
       <c r="X4" t="n">
-        <v>-21.1273</v>
+        <v>-17.9512</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. LOBACO MUÑOZ</t>
+          <t>G. PARHAM II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D5" t="n">
-        <v>24.9732</v>
+        <v>25.8296</v>
       </c>
       <c r="E5" t="n">
-        <v>5.796000000000001</v>
+        <v>-1.125200000000003</v>
       </c>
       <c r="F5" t="n">
-        <v>19.1774</v>
+        <v>26.9552</v>
       </c>
       <c r="G5" t="n">
-        <v>1.528900000000002</v>
+        <v>14.1734</v>
       </c>
       <c r="H5" t="n">
-        <v>-8.369400000000001</v>
+        <v>-1.6961</v>
       </c>
       <c r="I5" t="n">
-        <v>9.898300000000001</v>
+        <v>15.8694</v>
       </c>
       <c r="J5" t="n">
-        <v>33.4754</v>
+        <v>44.0734</v>
       </c>
       <c r="K5" t="n">
-        <v>12.0736</v>
+        <v>16.5117</v>
       </c>
       <c r="L5" t="n">
-        <v>21.402</v>
+        <v>27.5615</v>
       </c>
       <c r="M5" t="n">
-        <v>-31.9465</v>
+        <v>-29.9001</v>
       </c>
       <c r="N5" t="n">
-        <v>-20.4432</v>
+        <v>-18.2079</v>
       </c>
       <c r="O5" t="n">
-        <v>-11.5034</v>
+        <v>-11.692</v>
       </c>
       <c r="P5" t="n">
-        <v>18.4882</v>
+        <v>-7.178000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>-44.3713</v>
+        <v>-74.60469999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>62.8595</v>
+        <v>67.4272</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3995999999999996</v>
+        <v>5.7535</v>
       </c>
       <c r="T5" t="n">
-        <v>-5.8157</v>
+        <v>-0.6208000000000004</v>
       </c>
       <c r="U5" t="n">
-        <v>6.2154</v>
+        <v>6.3749</v>
       </c>
       <c r="V5" t="n">
-        <v>4.5565</v>
+        <v>13.0804</v>
       </c>
       <c r="W5" t="n">
-        <v>22.5076</v>
+        <v>30.0272</v>
       </c>
       <c r="X5" t="n">
-        <v>-17.9512</v>
+        <v>-16.9465</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>19.2885</v>
+        <v>19.0502</v>
       </c>
       <c r="E6" t="n">
-        <v>15.16</v>
+        <v>13.5088</v>
       </c>
       <c r="F6" t="n">
-        <v>4.1287</v>
+        <v>5.5414</v>
       </c>
       <c r="G6" t="n">
         <v>12.4633</v>
@@ -922,13 +922,13 @@
         <v>9.135</v>
       </c>
       <c r="S6" t="n">
-        <v>3.0127</v>
+        <v>2.7742</v>
       </c>
       <c r="T6" t="n">
-        <v>3.3082</v>
+        <v>1.6572</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2956</v>
+        <v>1.1173</v>
       </c>
       <c r="V6" t="n">
         <v>0.1149</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. SHELIST</t>
+          <t>D. DUSCAK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>3.846899999999998</v>
+        <v>16.5932</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1497</v>
+        <v>8.0267</v>
       </c>
       <c r="F7" t="n">
-        <v>1.697300000000002</v>
+        <v>8.5663</v>
       </c>
       <c r="G7" t="n">
-        <v>1.291500000000001</v>
+        <v>7.136500000000002</v>
       </c>
       <c r="H7" t="n">
-        <v>8.260400000000001</v>
+        <v>-10.8027</v>
       </c>
       <c r="I7" t="n">
-        <v>-6.968699999999999</v>
+        <v>17.9393</v>
       </c>
       <c r="J7" t="n">
-        <v>25.1149</v>
+        <v>36.9334</v>
       </c>
       <c r="K7" t="n">
-        <v>22.921</v>
+        <v>7.074400000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>2.193900000000001</v>
+        <v>29.8593</v>
       </c>
       <c r="M7" t="n">
-        <v>-23.8234</v>
+        <v>-29.7968</v>
       </c>
       <c r="N7" t="n">
-        <v>-14.6607</v>
+        <v>-17.8766</v>
       </c>
       <c r="O7" t="n">
-        <v>-9.162600000000001</v>
+        <v>-11.92</v>
       </c>
       <c r="P7" t="n">
-        <v>3.4799</v>
+        <v>6.090199999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>-40.0209</v>
+        <v>-49.374</v>
       </c>
       <c r="R7" t="n">
-        <v>43.501</v>
+        <v>55.46409999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>9.555400000000001</v>
+        <v>1.9175</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2382</v>
+        <v>-3.2323</v>
       </c>
       <c r="U7" t="n">
-        <v>6.3167</v>
+        <v>5.1499</v>
       </c>
       <c r="V7" t="n">
-        <v>-10.4805</v>
+        <v>1.4485</v>
       </c>
       <c r="W7" t="n">
-        <v>13.817</v>
+        <v>23.6995</v>
       </c>
       <c r="X7" t="n">
-        <v>-24.2973</v>
+        <v>-22.2509</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. DUSCAK</t>
+          <t>A. FAURE RIBES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D8" t="n">
-        <v>3.2651</v>
+        <v>13.346</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.022</v>
+        <v>4.205199999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>4.2868</v>
+        <v>9.140999999999998</v>
       </c>
       <c r="G8" t="n">
-        <v>7.136500000000002</v>
+        <v>19.4361</v>
       </c>
       <c r="H8" t="n">
-        <v>-10.8027</v>
+        <v>13.358</v>
       </c>
       <c r="I8" t="n">
-        <v>17.9393</v>
+        <v>6.0782</v>
       </c>
       <c r="J8" t="n">
-        <v>36.9334</v>
+        <v>38.2164</v>
       </c>
       <c r="K8" t="n">
-        <v>7.074400000000001</v>
+        <v>25.072</v>
       </c>
       <c r="L8" t="n">
-        <v>29.8593</v>
+        <v>13.1438</v>
       </c>
       <c r="M8" t="n">
-        <v>-29.7968</v>
+        <v>-18.7801</v>
       </c>
       <c r="N8" t="n">
-        <v>-17.8766</v>
+        <v>-11.7141</v>
       </c>
       <c r="O8" t="n">
-        <v>-11.92</v>
+        <v>-7.0662</v>
       </c>
       <c r="P8" t="n">
-        <v>6.090199999999999</v>
+        <v>-10.8754</v>
       </c>
       <c r="Q8" t="n">
-        <v>-49.374</v>
+        <v>-50.2438</v>
       </c>
       <c r="R8" t="n">
-        <v>55.46409999999999</v>
+        <v>39.3683</v>
       </c>
       <c r="S8" t="n">
-        <v>-11.4106</v>
+        <v>14.9711</v>
       </c>
       <c r="T8" t="n">
-        <v>-12.281</v>
+        <v>5.291300000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8703000000000003</v>
+        <v>9.679500000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4485</v>
+        <v>-10.1856</v>
       </c>
       <c r="W8" t="n">
-        <v>23.6995</v>
+        <v>10.9412</v>
       </c>
       <c r="X8" t="n">
-        <v>-22.2509</v>
+        <v>-21.1273</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. PARHAM II</t>
+          <t>D. SHELIST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5348000000000002</v>
+        <v>2.531100000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-19.5257</v>
+        <v>-0.09629999999999983</v>
       </c>
       <c r="F9" t="n">
-        <v>20.0607</v>
+        <v>2.627099999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>14.1734</v>
+        <v>1.291500000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6961</v>
+        <v>8.260400000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>15.8694</v>
+        <v>-6.968699999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>44.0734</v>
+        <v>25.1149</v>
       </c>
       <c r="K9" t="n">
-        <v>16.5117</v>
+        <v>22.921</v>
       </c>
       <c r="L9" t="n">
-        <v>27.5615</v>
+        <v>2.193900000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-29.9001</v>
+        <v>-23.8234</v>
       </c>
       <c r="N9" t="n">
-        <v>-18.2079</v>
+        <v>-14.6607</v>
       </c>
       <c r="O9" t="n">
-        <v>-11.692</v>
+        <v>-9.162600000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>-7.178000000000001</v>
+        <v>3.4799</v>
       </c>
       <c r="Q9" t="n">
-        <v>-74.60469999999999</v>
+        <v>-40.0209</v>
       </c>
       <c r="R9" t="n">
-        <v>67.4272</v>
+        <v>43.501</v>
       </c>
       <c r="S9" t="n">
-        <v>-19.5409</v>
+        <v>8.2394</v>
       </c>
       <c r="T9" t="n">
-        <v>-19.0211</v>
+        <v>0.9928999999999998</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5202999999999999</v>
+        <v>7.2465</v>
       </c>
       <c r="V9" t="n">
-        <v>13.0804</v>
+        <v>-10.4805</v>
       </c>
       <c r="W9" t="n">
-        <v>30.0272</v>
+        <v>13.817</v>
       </c>
       <c r="X9" t="n">
-        <v>-16.9465</v>
+        <v>-24.2973</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.7228</v>
+        <v>-4.963500000000002</v>
       </c>
       <c r="E10" t="n">
-        <v>-11.2435</v>
+        <v>-8.9397</v>
       </c>
       <c r="F10" t="n">
-        <v>4.5205</v>
+        <v>3.9764</v>
       </c>
       <c r="G10" t="n">
         <v>-12.4917</v>
@@ -1234,13 +1234,13 @@
         <v>17.4003</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4882</v>
+        <v>3.2473</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.091</v>
+        <v>0.2126999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>3.5789</v>
+        <v>3.0345</v>
       </c>
       <c r="V10" t="n">
         <v>3.410499999999999</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. GONZALEZ LONGARELA</t>
+          <t>F. NWAOKORIE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D11" t="n">
-        <v>-12.0954</v>
+        <v>-10.2622</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.7033</v>
+        <v>-33.5429</v>
       </c>
       <c r="F11" t="n">
-        <v>-7.3925</v>
+        <v>23.281</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.9118</v>
+        <v>-37.9117</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.0027</v>
+        <v>-2.3937</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.9092</v>
+        <v>-35.5182</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.2097</v>
+        <v>-11.9448</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3524999999999999</v>
+        <v>16.1725</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.857699999999999</v>
+        <v>-28.1176</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.7023</v>
+        <v>-25.9667</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.6504</v>
+        <v>-18.5663</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.0519</v>
+        <v>-7.4002</v>
       </c>
       <c r="P11" t="n">
-        <v>1.9576</v>
+        <v>18.0529</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.5676</v>
+        <v>-37.4107</v>
       </c>
       <c r="R11" t="n">
-        <v>6.525099999999999</v>
+        <v>55.4642</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2756000000000001</v>
+        <v>10.5579</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3366000000000001</v>
+        <v>3.9779</v>
       </c>
       <c r="U11" t="n">
-        <v>0.06100000000000008</v>
+        <v>6.5801</v>
       </c>
       <c r="V11" t="n">
-        <v>-5.8658</v>
+        <v>-0.9615999999999991</v>
       </c>
       <c r="W11" t="n">
-        <v>3.4106</v>
+        <v>11.8346</v>
       </c>
       <c r="X11" t="n">
-        <v>-9.276499999999999</v>
+        <v>-12.7962</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. NWAOKORIE</t>
+          <t>P. GONZALEZ LONGARELA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>-14.6503</v>
+        <v>-11.8821</v>
       </c>
       <c r="E12" t="n">
-        <v>-35.3784</v>
+        <v>-5.1935</v>
       </c>
       <c r="F12" t="n">
-        <v>20.7276</v>
+        <v>-6.688600000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-37.9117</v>
+        <v>-7.9118</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.3937</v>
+        <v>-3.0027</v>
       </c>
       <c r="I12" t="n">
-        <v>-35.5182</v>
+        <v>-4.9092</v>
       </c>
       <c r="J12" t="n">
-        <v>-11.9448</v>
+        <v>-3.2097</v>
       </c>
       <c r="K12" t="n">
-        <v>16.1725</v>
+        <v>-0.3524999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-28.1176</v>
+        <v>-2.857699999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-25.9667</v>
+        <v>-4.7023</v>
       </c>
       <c r="N12" t="n">
-        <v>-18.5663</v>
+        <v>-2.6504</v>
       </c>
       <c r="O12" t="n">
-        <v>-7.4002</v>
+        <v>-2.0519</v>
       </c>
       <c r="P12" t="n">
-        <v>18.0529</v>
+        <v>1.9576</v>
       </c>
       <c r="Q12" t="n">
-        <v>-37.4107</v>
+        <v>-4.5676</v>
       </c>
       <c r="R12" t="n">
-        <v>55.4642</v>
+        <v>6.525099999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>6.1696</v>
+        <v>-0.06179999999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>2.1431</v>
+        <v>-0.8267</v>
       </c>
       <c r="U12" t="n">
-        <v>4.0267</v>
+        <v>0.765</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9615999999999991</v>
+        <v>-5.8658</v>
       </c>
       <c r="W12" t="n">
-        <v>11.8346</v>
+        <v>3.4106</v>
       </c>
       <c r="X12" t="n">
-        <v>-12.7962</v>
+        <v>-9.276499999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>27</v>
       </c>
       <c r="D13" t="n">
-        <v>-22.8773</v>
+        <v>-14.4986</v>
       </c>
       <c r="E13" t="n">
-        <v>-19.2161</v>
+        <v>-14.0177</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.6614</v>
+        <v>-0.4812000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-24.5401</v>
@@ -1468,13 +1468,13 @@
         <v>27.6229</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.825100000000001</v>
+        <v>-1.4467</v>
       </c>
       <c r="T13" t="n">
-        <v>-8.095600000000001</v>
+        <v>-2.8971</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.7295</v>
+        <v>1.4507</v>
       </c>
       <c r="V13" t="n">
         <v>4.310600000000001</v>
@@ -1501,22 +1501,22 @@
         <v>32</v>
       </c>
       <c r="D14" t="n">
-        <v>149.0831</v>
+        <v>170.8676</v>
       </c>
       <c r="E14" t="n">
-        <v>30.95970000000001</v>
+        <v>39.97649999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>118.1228</v>
+        <v>130.8913</v>
       </c>
       <c r="G14" t="n">
         <v>44.5739</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7180999999999997</v>
+        <v>-0.7181000000000006</v>
       </c>
       <c r="I14" t="n">
-        <v>45.29180000000001</v>
+        <v>45.29179999999998</v>
       </c>
       <c r="J14" t="n">
         <v>283.4376</v>
@@ -1534,7 +1534,7 @@
         <v>-144.9484</v>
       </c>
       <c r="O14" t="n">
-        <v>-93.91460000000001</v>
+        <v>-93.91459999999999</v>
       </c>
       <c r="P14" t="n">
         <v>14.1369</v>
@@ -1546,16 +1546,16 @@
         <v>482.8633</v>
       </c>
       <c r="S14" t="n">
-        <v>69.79520000000001</v>
+        <v>91.5788</v>
       </c>
       <c r="T14" t="n">
-        <v>14.026</v>
+        <v>23.043</v>
       </c>
       <c r="U14" t="n">
-        <v>55.76799999999999</v>
+        <v>68.5369</v>
       </c>
       <c r="V14" t="n">
-        <v>20.5755</v>
+        <v>20.57549999999999</v>
       </c>
       <c r="W14" t="n">
         <v>202.2216</v>
